--- a/fhir/StructureDefinition-ehealth-documentreference.xlsx
+++ b/fhir/StructureDefinition-ehealth-documentreference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -373,7 +373,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1253,7 +1253,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1337,7 +1337,7 @@
     <t>Document Format Codes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/formatcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/formatcodes|4.0.1</t>
   </si>
   <si>
     <t>Composition.meta.profile</t>
@@ -1469,7 +1469,7 @@
     <t>XDS Facility Type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes|4.0.1</t>
   </si>
   <si>
     <t>usually from a mapping to a local ValueSet</t>
@@ -1502,7 +1502,7 @@
     <t>Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>DocumentEntry.practiceSettingCode</t>
@@ -1527,7 +1527,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>

--- a/fhir/StructureDefinition-ehealth-documentreference.xlsx
+++ b/fhir/StructureDefinition-ehealth-documentreference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-documentreference.xlsx
+++ b/fhir/StructureDefinition-ehealth-documentreference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-documentreference.xlsx
+++ b/fhir/StructureDefinition-ehealth-documentreference.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2827" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2827" uniqueCount="496">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -593,6 +593,12 @@
   </si>
   <si>
     <t>function</t>
+  </si>
+  <si>
+    <t>The function of the participant</t>
+  </si>
+  <si>
+    <t>The code defining the function of the participant.</t>
   </si>
   <si>
     <t>DocumentReference.extension:participant.extension:function.id</t>
@@ -3897,10 +3903,10 @@
         <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3989,10 +3995,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4110,10 +4116,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4231,10 +4237,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4260,13 +4266,13 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4316,7 +4322,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>91</v>
@@ -4354,10 +4360,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4380,13 +4386,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4413,11 +4419,11 @@
         <v>78</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>78</v>
@@ -4435,7 +4441,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4473,13 +4479,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>177</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -4504,10 +4510,10 @@
         <v>136</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4596,10 +4602,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4717,10 +4723,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4838,10 +4844,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4867,13 +4873,13 @@
         <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4881,7 +4887,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>78</v>
@@ -4923,7 +4929,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -4961,10 +4967,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4987,13 +4993,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5044,7 +5050,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5082,13 +5088,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>177</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>78</v>
@@ -5113,10 +5119,10 @@
         <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5205,10 +5211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5326,10 +5332,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5447,10 +5453,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5476,13 +5482,13 @@
         <v>105</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5490,7 +5496,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>78</v>
@@ -5532,7 +5538,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>91</v>
@@ -5570,10 +5576,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5599,10 +5605,10 @@
         <v>171</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5653,7 +5659,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5691,10 +5697,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5720,13 +5726,13 @@
         <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5734,7 +5740,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
@@ -5776,7 +5782,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>91</v>
@@ -5814,10 +5820,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5840,13 +5846,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5897,7 +5903,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5935,13 +5941,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
@@ -5963,13 +5969,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6058,13 +6064,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
@@ -6086,13 +6092,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6181,10 +6187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6210,16 +6216,16 @@
         <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>181</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6268,7 +6274,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6306,10 +6312,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6332,19 +6338,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6393,7 +6399,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6408,33 +6414,33 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6457,13 +6463,13 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6514,7 +6520,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6529,33 +6535,33 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6581,13 +6587,13 @@
         <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6613,13 +6619,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -6637,7 +6643,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6652,33 +6658,33 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6704,13 +6710,13 @@
         <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6736,13 +6742,13 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -6760,7 +6766,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6778,19 +6784,19 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>78</v>
@@ -6798,10 +6804,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6824,16 +6830,16 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6859,11 +6865,11 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -6881,7 +6887,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6896,37 +6902,37 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6945,16 +6951,16 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6980,11 +6986,11 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -7002,7 +7008,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7020,30 +7026,30 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7066,13 +7072,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7123,7 +7129,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7138,37 +7144,37 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7187,16 +7193,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7246,7 +7252,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7261,19 +7267,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>78</v>
@@ -7284,10 +7290,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7310,16 +7316,16 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7369,7 +7375,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7384,33 +7390,33 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7433,16 +7439,16 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7492,7 +7498,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7507,33 +7513,33 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7556,16 +7562,16 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7615,7 +7621,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7630,13 +7636,13 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7653,10 +7659,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7679,16 +7685,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7738,7 +7744,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7756,10 +7762,10 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7771,15 +7777,15 @@
         <v>78</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7897,10 +7903,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8020,14 +8026,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8049,16 +8055,16 @@
         <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>181</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8107,7 +8113,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8145,10 +8151,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8174,13 +8180,13 @@
         <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8206,13 +8212,13 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -8230,7 +8236,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>91</v>
@@ -8248,10 +8254,10 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8263,15 +8269,15 @@
         <v>78</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8294,13 +8300,13 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8351,7 +8357,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>91</v>
@@ -8369,10 +8375,10 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8384,15 +8390,15 @@
         <v>78</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8418,16 +8424,16 @@
         <v>171</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8476,7 +8482,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8497,7 +8503,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8506,18 +8512,18 @@
         <v>78</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8540,19 +8546,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8577,13 +8583,13 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8601,7 +8607,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8619,30 +8625,30 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8665,13 +8671,13 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8722,7 +8728,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -8740,10 +8746,10 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8760,10 +8766,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8881,10 +8887,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9004,14 +9010,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9033,16 +9039,16 @@
         <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>181</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9091,7 +9097,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9129,10 +9135,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9155,13 +9161,13 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9212,7 +9218,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9230,30 +9236,30 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9276,16 +9282,16 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9314,10 +9320,10 @@
         <v>115</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>78</v>
@@ -9335,7 +9341,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9353,13 +9359,13 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9368,15 +9374,15 @@
         <v>78</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9399,16 +9405,16 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9458,7 +9464,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9479,7 +9485,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9496,10 +9502,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9617,10 +9623,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9740,14 +9746,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9769,16 +9775,16 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>181</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9827,7 +9833,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9865,10 +9871,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9891,13 +9897,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9948,7 +9954,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9963,19 +9969,19 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>78</v>
@@ -9986,10 +9992,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10012,16 +10018,16 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10047,13 +10053,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -10071,7 +10077,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10089,10 +10095,10 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
@@ -10104,15 +10110,15 @@
         <v>78</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10135,13 +10141,13 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10192,7 +10198,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10210,13 +10216,13 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -10225,15 +10231,15 @@
         <v>78</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10256,13 +10262,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10289,13 +10295,13 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -10313,7 +10319,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10331,13 +10337,13 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10346,15 +10352,15 @@
         <v>78</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10377,19 +10383,19 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10414,13 +10420,13 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10438,7 +10444,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10456,13 +10462,13 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10471,15 +10477,15 @@
         <v>78</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10502,13 +10508,13 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10559,7 +10565,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10577,13 +10583,13 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10592,15 +10598,15 @@
         <v>78</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10623,16 +10629,16 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10682,7 +10688,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10700,13 +10706,13 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10715,7 +10721,7 @@
         <v>78</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/StructureDefinition-ehealth-documentreference.xlsx
+++ b/fhir/StructureDefinition-ehealth-documentreference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-documentreference.xlsx
+++ b/fhir/StructureDefinition-ehealth-documentreference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-documentreference.xlsx
+++ b/fhir/StructureDefinition-ehealth-documentreference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
